--- a/data/data_meta-analysis.xlsx
+++ b/data/data_meta-analysis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10720"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11023"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uporto.sharepoint.com/sites/Project-M2Child-Specific/Documentos Partilhados/Specific/M2Child ~things~/09) Dados/R/Meta-Analysis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/teresacorreiadesa/R/Meta-Analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2199" documentId="8_{5FF1B46A-1F9C-EA4D-A4A4-F561C8B53FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7B737627-BAE5-7B4D-B15B-9D60C7E575DA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E205C64-2A6D-1645-B077-6415CB7EF189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20060" xr2:uid="{37AE9339-BB2C-3744-A9A3-4F75285B30BC}"/>
+    <workbookView xWindow="-38400" yWindow="-21000" windowWidth="38400" windowHeight="19420" xr2:uid="{37AE9339-BB2C-3744-A9A3-4F75285B30BC}"/>
   </bookViews>
   <sheets>
     <sheet name="DOPAMINE" sheetId="1" r:id="rId1"/>
@@ -50,6 +50,7 @@
     <author>tc={82433E5C-D557-7A42-B145-EFF546BAC852}</author>
     <author>tc={C904814F-85BF-9C4D-961A-6F2A41DBB093}</author>
     <author>tc={37BDA354-75BD-DC4B-953A-70A240B20C1F}</author>
+    <author>tc={BA6E313E-BF4E-D640-8A1A-7A71E66F4E11}</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0" xr:uid="{9582C091-E79B-9848-B407-EC1F2E583F24}">
@@ -100,6 +101,16 @@
     The standard deviation in the control group.</t>
       </text>
     </comment>
+    <comment ref="M1" authorId="6" shapeId="0" xr:uid="{BA6E313E-BF4E-D640-8A1A-7A71E66F4E11}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    for cleaner subgroup analysis plots later on:
+- ADHD doesn't take med = No (have taken in the past or are medication-naive)
+- ADHD takes med = Yes (all or almost all)</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -113,6 +124,8 @@
     <author>tc={4BA2FBB7-76C0-AE46-BC7A-A98C0068D1FA}</author>
     <author>tc={DF0387CF-6158-664A-BCCA-889105AAE9F2}</author>
     <author>tc={BBDA1B18-269C-B14A-8959-C9B8BC608A36}</author>
+    <author>tc={24762B07-76B0-404E-A83D-A1906C8F129D}</author>
+    <author>Teresa Correia de Sá</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0" xr:uid="{2209A2AA-A918-3941-A3DA-B97925BB2CE6}">
@@ -163,6 +176,168 @@
     The standard deviation in the control group.</t>
       </text>
     </comment>
+    <comment ref="M1" authorId="6" shapeId="0" xr:uid="{24762B07-76B0-404E-A83D-A1906C8F129D}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    for later subgroup analysis plots:
+- ADHD doesn't take med = No (have taken in the past or are medication-naive)
+- ADHD takes med = Yes (all or almost all)</t>
+      </text>
+    </comment>
+    <comment ref="D4" authorId="7" shapeId="0" xr:uid="{20669179-E8D2-D64B-8E4D-8407A5C6FEAB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Teresa Correia de Sá:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>SEM convertion to SD</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G4" authorId="7" shapeId="0" xr:uid="{5E7EAE69-D417-6340-A355-DA76FD1F992A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Teresa Correia de Sá:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>SEM convertion to SD</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D14" authorId="7" shapeId="0" xr:uid="{F4A7582A-6D34-634C-9714-A33E34A2D285}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Teresa Correia de Sá:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>SEM convertion to SD</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G14" authorId="7" shapeId="0" xr:uid="{087013E3-FC91-F448-85D4-C3B2CCD03728}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Teresa Correia de Sá:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>SEM convertion to SD</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -176,6 +351,8 @@
     <author>tc={B92250FA-778F-6846-BF26-9BA41280E767}</author>
     <author>tc={2C80292C-C258-FF4E-B785-7DCB60FEF077}</author>
     <author>tc={7D08D5B7-DC08-DE41-977A-FCB6F29F9EBE}</author>
+    <author>tc={229FAAD6-9652-074A-BDC1-E024165C877C}</author>
+    <author>Teresa Correia de Sá</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0" xr:uid="{8C7432B5-7D07-BE4A-ADBD-7942CF9ED25A}">
@@ -226,6 +403,188 @@
     The standard deviation in the control group.</t>
       </text>
     </comment>
+    <comment ref="M1" authorId="6" shapeId="0" xr:uid="{229FAAD6-9652-074A-BDC1-E024165C877C}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    for later subgroup analysis plots:
+- ADHD doesn't take med = No (have taken in the past or are medication-naive)
+- ADHD takes med = Yes (all or almost all)</t>
+      </text>
+    </comment>
+    <comment ref="D5" authorId="7" shapeId="0" xr:uid="{4BBB9FA0-52DC-7049-A5C5-D9FC635CB2A7}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Teresa Correia de Sá:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>SEM convertion to SD</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G5" authorId="7" shapeId="0" xr:uid="{28548280-CE16-754B-9E15-5D8E318B8914}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Teresa Correia de Sá:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>SEM convertion to SD</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D17" authorId="7" shapeId="0" xr:uid="{6B338901-F8C4-E34F-A7AC-8EDF862CEF7C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Teresa Correia de Sá:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>SEM convertion to SD</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G17" authorId="7" shapeId="0" xr:uid="{DB412C80-4F20-F546-9A3D-79A9844FA5BB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Teresa Correia de Sá:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>SEM convertion to SD</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -239,6 +598,8 @@
     <author>tc={95308AD9-4BDF-234F-8019-7F50E5FFE4D0}</author>
     <author>tc={B0009F5A-8E73-6448-94EF-8738545B82C5}</author>
     <author>tc={AFF2E13B-B9F2-5C49-8074-7D9788A72720}</author>
+    <author>tc={584ABAA7-E4B2-7B41-A591-A05BC065679B}</author>
+    <author>Teresa Correia de Sá</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0" xr:uid="{9FE70FA1-0F0E-4F46-AE34-81FAB30D0237}">
@@ -289,6 +650,92 @@
     The standard deviation in the control group.</t>
       </text>
     </comment>
+    <comment ref="M1" authorId="6" shapeId="0" xr:uid="{584ABAA7-E4B2-7B41-A591-A05BC065679B}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    for later subgroup analysis plots:
+- ADHD doesn't take med = No (have taken in the past or are medication-naive)
+- ADHD takes med = Yes (all or almost all)</t>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="7" shapeId="0" xr:uid="{CFFA4B41-F3C3-7146-BC78-6BE5F79D51B6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Teresa Correia de Sá:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>SEM convertion to SD</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G7" authorId="7" shapeId="0" xr:uid="{2C24FC75-192C-F74B-9DC8-475E743CB1D8}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Teresa Correia de Sá:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <color rgb="FF000000"/>
+            <rFont val="Aptos Narrow"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>SEM convertion to SD</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -302,6 +749,7 @@
     <author>tc={BCD5EB0A-5FEA-7943-AA76-0F608E1D5E24}</author>
     <author>tc={A513AF50-C63A-BD43-BAD1-844D939B3159}</author>
     <author>tc={DC2A0D2E-59D3-514E-B774-F4B5E881E37D}</author>
+    <author>tc={DAB90153-C344-2F4E-9256-29561116DAEE}</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0" xr:uid="{E102B171-C78D-C341-9C14-364DE2DBED86}">
@@ -352,6 +800,16 @@
     The standard deviation in the control group.</t>
       </text>
     </comment>
+    <comment ref="L1" authorId="6" shapeId="0" xr:uid="{DAB90153-C344-2F4E-9256-29561116DAEE}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    for later subgroup analysis plots:
+- ADHD doesn't take med = No (have taken in the past or are medication-naive)
+- ADHD takes med = Yes (but not all)</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -365,6 +823,7 @@
     <author>tc={DC4F7DAE-7C45-D74D-A923-8E39CF181CF6}</author>
     <author>tc={0AAA84C3-35F3-4F48-A6EF-45793CFEF4CB}</author>
     <author>tc={826BFB02-C609-5744-B4B4-51285D20839B}</author>
+    <author>tc={6C5786C7-36A3-7348-9C15-908D1DA5B5D2}</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0" xr:uid="{476E1485-BE3D-114C-81D9-1DD345073904}">
@@ -415,6 +874,16 @@
     The standard deviation in the control group.</t>
       </text>
     </comment>
+    <comment ref="L1" authorId="6" shapeId="0" xr:uid="{6C5786C7-36A3-7348-9C15-908D1DA5B5D2}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    for later subgroup analysis plots:
+- ADHD doesn't take med = No (have taken in the past or are medication-naive)
+- ADHD takes med = Yes (but not all)</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -428,6 +897,7 @@
     <author>tc={F4E9DBBE-9159-484B-9887-676C45009A22}</author>
     <author>tc={C85FEBCA-8367-C541-9066-A958F5FD1144}</author>
     <author>tc={BFA83703-16AB-D14A-8FE5-2EFF29672654}</author>
+    <author>tc={A31B8CA7-3F77-0E49-84BD-EC19CE214978}</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0" xr:uid="{B1F0EFEE-5A95-804D-9FFE-62CDE6A56A3C}">
@@ -478,12 +948,22 @@
     The standard deviation in the control group.</t>
       </text>
     </comment>
+    <comment ref="M1" authorId="6" shapeId="0" xr:uid="{A31B8CA7-3F77-0E49-84BD-EC19CE214978}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    for later subgroup analysis plots:
+- ADHD doesn't take med = No (have taken in the past or are medication-naive)
+- ADHD takes med = Yes (but not all)</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="69">
   <si>
     <t>Study</t>
   </si>
@@ -536,22 +1016,10 @@
     <t>StudyQuality</t>
   </si>
   <si>
-    <t>Other</t>
-  </si>
-  <si>
     <t>UrineProtocol</t>
   </si>
   <si>
     <t>BloodComponents</t>
-  </si>
-  <si>
-    <t>DSM-IV or DSM-IV-TR or DSM-5</t>
-  </si>
-  <si>
-    <t>24-hr collection</t>
-  </si>
-  <si>
-    <t>&lt;24-hr collection</t>
   </si>
   <si>
     <t>Whole blood</t>
@@ -566,43 +1034,10 @@
     <t>Male</t>
   </si>
   <si>
-    <t>Both</t>
-  </si>
-  <si>
-    <t>Western</t>
-  </si>
-  <si>
-    <t>Eastern</t>
-  </si>
-  <si>
     <t>HPLC</t>
   </si>
   <si>
-    <t>Fair or Good</t>
-  </si>
-  <si>
-    <t>Very poor or Poor</t>
-  </si>
-  <si>
     <t>Moriarty 2011</t>
-  </si>
-  <si>
-    <t>Comings 1990</t>
-  </si>
-  <si>
-    <t>Novkovic 2009</t>
-  </si>
-  <si>
-    <t>Molina-Carballo 2013</t>
-  </si>
-  <si>
-    <t>Wang 2018</t>
-  </si>
-  <si>
-    <t>Jawad 2019</t>
-  </si>
-  <si>
-    <t>Raghavan 2022</t>
   </si>
   <si>
     <t>Hanna 1996b</t>
@@ -614,28 +1049,16 @@
     <t>Shekim 1987</t>
   </si>
   <si>
-    <t>Oades 1998</t>
-  </si>
-  <si>
     <t>Kusaga 2002</t>
   </si>
   <si>
     <t>Bos 2015</t>
   </si>
   <si>
-    <t>Ionescu 1990</t>
-  </si>
-  <si>
     <t>Hanna 1996a</t>
   </si>
   <si>
     <t>Dvoráková 2007</t>
-  </si>
-  <si>
-    <t>Alsen 2015</t>
-  </si>
-  <si>
-    <t>Xiong 2021</t>
   </si>
   <si>
     <t>Rapoport 1978</t>
@@ -650,34 +1073,10 @@
     <t>Anderson 2000</t>
   </si>
   <si>
-    <t>Nagel-Hiemke 1984</t>
-  </si>
-  <si>
-    <t>Girardi 1995</t>
-  </si>
-  <si>
-    <t>Mikkelsen 1981</t>
-  </si>
-  <si>
-    <t>Oades 2010a</t>
-  </si>
-  <si>
     <t>Rapoport 1970</t>
   </si>
   <si>
-    <t>Irwin 1981</t>
-  </si>
-  <si>
     <t>ADHDtakesMed</t>
-  </si>
-  <si>
-    <t>Yes, but not all</t>
-  </si>
-  <si>
-    <t>No (have taken in the past or are medication-naive)</t>
-  </si>
-  <si>
-    <t>Yes (all or almost all)</t>
   </si>
   <si>
     <t>LC-MS</t>
@@ -689,14 +1088,95 @@
     <t>Spectrofluorimetry</t>
   </si>
   <si>
-    <t>Yes (but not all)</t>
+    <t>DSM-IV/DSM-IV-TR/DSM-5</t>
+  </si>
+  <si>
+    <t>Ionescu 1990 *</t>
+  </si>
+  <si>
+    <t>Alsen 2015 *</t>
+  </si>
+  <si>
+    <t>Xiong 2021 *</t>
+  </si>
+  <si>
+    <t>Nemet 2024 *</t>
+  </si>
+  <si>
+    <t>Nagel-Hiemke 1984 *</t>
+  </si>
+  <si>
+    <t>Girardi 1995 *</t>
+  </si>
+  <si>
+    <t>Oades 1998 *</t>
+  </si>
+  <si>
+    <t>Mikkelsen 1981 *</t>
+  </si>
+  <si>
+    <t>Irwin 1981 *</t>
+  </si>
+  <si>
+    <t>Comings 1990 *</t>
+  </si>
+  <si>
+    <t>Novkovic 2009 *</t>
+  </si>
+  <si>
+    <t>Molina-Carballo 2013 *</t>
+  </si>
+  <si>
+    <t>Wang 2018 *</t>
+  </si>
+  <si>
+    <t>Jawad 2019 *</t>
+  </si>
+  <si>
+    <t>Raghavan 2022 *</t>
+  </si>
+  <si>
+    <t>Oades 2010a *</t>
+  </si>
+  <si>
+    <t>24-hr urine collection</t>
+  </si>
+  <si>
+    <t>&lt;24-hr urine collection</t>
+  </si>
+  <si>
+    <t>Western country</t>
+  </si>
+  <si>
+    <t>Eastern country</t>
+  </si>
+  <si>
+    <t>Both sexes</t>
+  </si>
+  <si>
+    <t>Other assay method</t>
+  </si>
+  <si>
+    <t>Very poor or Poor quality</t>
+  </si>
+  <si>
+    <t>Fair or Good quality</t>
+  </si>
+  <si>
+    <t>Other diagnostic method</t>
+  </si>
+  <si>
+    <t>ADHD group doesn't take med</t>
+  </si>
+  <si>
+    <t>ADHD group takes med</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -751,6 +1231,25 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -778,9 +1277,29 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
@@ -790,7 +1309,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -829,352 +1348,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="128">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <right/>
-        <top/>
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Display"/>
-        <scheme val="major"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3143,6 +3339,338 @@
         <color theme="1"/>
         <name val="Aptos Narrow"/>
         <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <right/>
+        <top/>
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Display"/>
+        <scheme val="major"/>
       </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -3166,185 +3694,188 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DE330CD1-F409-6F42-93D5-0F0C9F3797DC}" name="Table1" displayName="Table1" ref="A1:P8" totalsRowShown="0" headerRowDxfId="127" dataDxfId="126">
-  <autoFilter ref="A1:P8" xr:uid="{DE330CD1-F409-6F42-93D5-0F0C9F3797DC}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P8">
-    <sortCondition ref="H1:H8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DE330CD1-F409-6F42-93D5-0F0C9F3797DC}" name="Table1" displayName="Table1" ref="A1:P9" totalsRowShown="0" headerRowDxfId="108" dataDxfId="107">
+  <autoFilter ref="A1:P9" xr:uid="{DE330CD1-F409-6F42-93D5-0F0C9F3797DC}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P9">
+    <sortCondition ref="H1:H9"/>
   </sortState>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{E3389603-7E5D-314B-8C36-996CE6E564D5}" name="Study" dataDxfId="125"/>
-    <tableColumn id="2" xr3:uid="{565FE746-3F83-0447-8F6C-A9DB07F9F49F}" name="n.e." dataDxfId="124"/>
-    <tableColumn id="3" xr3:uid="{6A250A00-202C-8D4C-BDC3-AF389B550019}" name="mean.e." dataDxfId="123"/>
-    <tableColumn id="4" xr3:uid="{FAC1AF6E-F680-2749-AE34-1BE3CB476E1C}" name="sd.e." dataDxfId="122"/>
-    <tableColumn id="5" xr3:uid="{1A1313D8-99A0-7C48-899F-459FD50FE095}" name="n.c." dataDxfId="121"/>
-    <tableColumn id="6" xr3:uid="{33BB7E8B-CD79-C541-998C-69B8EFD0DE3A}" name="mean.c." dataDxfId="120"/>
-    <tableColumn id="7" xr3:uid="{4B73B9BC-D190-874A-A8B4-B6EB6335B380}" name="sd.c." dataDxfId="119"/>
-    <tableColumn id="8" xr3:uid="{5BDF6C67-EC4C-2344-AFE7-FE8BB73D9041}" name="Sample" dataDxfId="118"/>
-    <tableColumn id="14" xr3:uid="{0D981AB0-F26E-6149-8A85-C1C31AD83B71}" name="UrineProtocol" dataDxfId="117"/>
-    <tableColumn id="15" xr3:uid="{37EF3ACA-9C6A-134E-98B9-77840E0DC058}" name="BloodComponents" dataDxfId="116"/>
-    <tableColumn id="10" xr3:uid="{B67A2CA9-DAD5-D340-BE55-EFB7F26A8B3F}" name="Country" dataDxfId="115"/>
-    <tableColumn id="12" xr3:uid="{8C2B75A2-6E92-4D4A-B9D8-A1BAFB01DE60}" name="Sex" dataDxfId="114"/>
-    <tableColumn id="16" xr3:uid="{676E8F99-A998-A049-B4BE-4D6F3B2874B8}" name="ADHDtakesMed" dataDxfId="113"/>
-    <tableColumn id="11" xr3:uid="{C6B71830-9B20-6D49-83AC-9CC4DF032190}" name="ADHDassess" dataDxfId="112"/>
-    <tableColumn id="13" xr3:uid="{61F5DCC4-FA91-5B48-A90E-99730B17F9E9}" name="AssayMethod" dataDxfId="111"/>
-    <tableColumn id="9" xr3:uid="{71F01CA4-EAF4-2D49-9070-F9C886E773B6}" name="StudyQuality" dataDxfId="110"/>
+    <tableColumn id="1" xr3:uid="{E3389603-7E5D-314B-8C36-996CE6E564D5}" name="Study" dataDxfId="106"/>
+    <tableColumn id="2" xr3:uid="{565FE746-3F83-0447-8F6C-A9DB07F9F49F}" name="n.e." dataDxfId="105"/>
+    <tableColumn id="3" xr3:uid="{6A250A00-202C-8D4C-BDC3-AF389B550019}" name="mean.e." dataDxfId="104"/>
+    <tableColumn id="4" xr3:uid="{FAC1AF6E-F680-2749-AE34-1BE3CB476E1C}" name="sd.e." dataDxfId="103"/>
+    <tableColumn id="5" xr3:uid="{1A1313D8-99A0-7C48-899F-459FD50FE095}" name="n.c." dataDxfId="102"/>
+    <tableColumn id="6" xr3:uid="{33BB7E8B-CD79-C541-998C-69B8EFD0DE3A}" name="mean.c." dataDxfId="101"/>
+    <tableColumn id="7" xr3:uid="{4B73B9BC-D190-874A-A8B4-B6EB6335B380}" name="sd.c." dataDxfId="100"/>
+    <tableColumn id="8" xr3:uid="{5BDF6C67-EC4C-2344-AFE7-FE8BB73D9041}" name="Sample" dataDxfId="99"/>
+    <tableColumn id="14" xr3:uid="{0D981AB0-F26E-6149-8A85-C1C31AD83B71}" name="UrineProtocol" dataDxfId="98"/>
+    <tableColumn id="15" xr3:uid="{37EF3ACA-9C6A-134E-98B9-77840E0DC058}" name="BloodComponents" dataDxfId="97"/>
+    <tableColumn id="10" xr3:uid="{B67A2CA9-DAD5-D340-BE55-EFB7F26A8B3F}" name="Country" dataDxfId="96"/>
+    <tableColumn id="12" xr3:uid="{8C2B75A2-6E92-4D4A-B9D8-A1BAFB01DE60}" name="Sex" dataDxfId="95"/>
+    <tableColumn id="16" xr3:uid="{676E8F99-A998-A049-B4BE-4D6F3B2874B8}" name="ADHDtakesMed" dataDxfId="94"/>
+    <tableColumn id="11" xr3:uid="{C6B71830-9B20-6D49-83AC-9CC4DF032190}" name="ADHDassess" dataDxfId="93"/>
+    <tableColumn id="13" xr3:uid="{61F5DCC4-FA91-5B48-A90E-99730B17F9E9}" name="AssayMethod" dataDxfId="92"/>
+    <tableColumn id="9" xr3:uid="{71F01CA4-EAF4-2D49-9070-F9C886E773B6}" name="StudyQuality" dataDxfId="91"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{82941E60-9FB8-9C4C-BA9B-4F2D47A3DF78}" name="Table2" displayName="Table2" ref="A1:P13" totalsRowShown="0" headerRowDxfId="109" dataDxfId="108">
-  <autoFilter ref="A1:P13" xr:uid="{82941E60-9FB8-9C4C-BA9B-4F2D47A3DF78}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P13">
-    <sortCondition ref="H1:H13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{82941E60-9FB8-9C4C-BA9B-4F2D47A3DF78}" name="Table2" displayName="Table2" ref="A1:P14" totalsRowShown="0" headerRowDxfId="90" dataDxfId="89">
+  <autoFilter ref="A1:P14" xr:uid="{82941E60-9FB8-9C4C-BA9B-4F2D47A3DF78}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P14">
+    <sortCondition ref="H1:H14"/>
   </sortState>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{82F409B2-E0F7-7845-BCC7-5FDEF107306D}" name="Study" dataDxfId="107"/>
-    <tableColumn id="2" xr3:uid="{B80D5F59-D1CE-664E-9473-958F65C9E37B}" name="n.e." dataDxfId="106"/>
-    <tableColumn id="3" xr3:uid="{00D8D376-0D0B-8C4A-ACC5-91AD2C0C09E3}" name="mean.e." dataDxfId="105"/>
-    <tableColumn id="4" xr3:uid="{D61CAE4B-A234-2E4B-A71A-3D598B890250}" name="sd.e." dataDxfId="104"/>
-    <tableColumn id="5" xr3:uid="{71227982-1AF1-7F40-8E3D-20792291FC20}" name="n.c." dataDxfId="103"/>
-    <tableColumn id="6" xr3:uid="{D36D9CDB-8E52-0F49-8765-9A4E446C03B5}" name="mean.c." dataDxfId="102"/>
-    <tableColumn id="7" xr3:uid="{345B07A4-A54E-854A-BBFA-2EBF59CFC775}" name="sd.c." dataDxfId="101"/>
-    <tableColumn id="8" xr3:uid="{6D331CE1-E4E9-5B47-98DF-776C72DEC2A4}" name="Sample" dataDxfId="100"/>
-    <tableColumn id="15" xr3:uid="{7A330C55-8CDE-0140-B84A-A88A9B073242}" name="UrineProtocol" dataDxfId="99"/>
-    <tableColumn id="14" xr3:uid="{FFC67209-2250-E746-B101-892855B7723E}" name="BloodComponents" dataDxfId="98"/>
-    <tableColumn id="9" xr3:uid="{D33BD4F6-DBB2-CB4B-BB20-3BF2C38C6B15}" name="Country" dataDxfId="97"/>
-    <tableColumn id="10" xr3:uid="{90B3A5BF-6BFB-1B47-9F2C-3B2E0DD27E9C}" name="Sex" dataDxfId="96"/>
-    <tableColumn id="16" xr3:uid="{790D0C3F-38B9-454C-B087-1E30344494A3}" name="ADHDtakesMed" dataDxfId="95"/>
-    <tableColumn id="11" xr3:uid="{E0938665-DA8D-7A47-8819-689E53C8E13D}" name="ADHDassess" dataDxfId="94"/>
-    <tableColumn id="12" xr3:uid="{64C2D0D2-8ADC-E44C-8D2D-EBFCFD68558C}" name="AssayMethod" dataDxfId="93"/>
-    <tableColumn id="13" xr3:uid="{8B3BF2BF-7462-0548-99A9-3E81F4AC0BCD}" name="StudyQuality" dataDxfId="92"/>
+    <tableColumn id="1" xr3:uid="{82F409B2-E0F7-7845-BCC7-5FDEF107306D}" name="Study" dataDxfId="88"/>
+    <tableColumn id="2" xr3:uid="{B80D5F59-D1CE-664E-9473-958F65C9E37B}" name="n.e." dataDxfId="87"/>
+    <tableColumn id="3" xr3:uid="{00D8D376-0D0B-8C4A-ACC5-91AD2C0C09E3}" name="mean.e." dataDxfId="86"/>
+    <tableColumn id="4" xr3:uid="{D61CAE4B-A234-2E4B-A71A-3D598B890250}" name="sd.e." dataDxfId="85"/>
+    <tableColumn id="5" xr3:uid="{71227982-1AF1-7F40-8E3D-20792291FC20}" name="n.c." dataDxfId="84"/>
+    <tableColumn id="6" xr3:uid="{D36D9CDB-8E52-0F49-8765-9A4E446C03B5}" name="mean.c." dataDxfId="83"/>
+    <tableColumn id="7" xr3:uid="{345B07A4-A54E-854A-BBFA-2EBF59CFC775}" name="sd.c." dataDxfId="82"/>
+    <tableColumn id="8" xr3:uid="{6D331CE1-E4E9-5B47-98DF-776C72DEC2A4}" name="Sample" dataDxfId="81"/>
+    <tableColumn id="15" xr3:uid="{7A330C55-8CDE-0140-B84A-A88A9B073242}" name="UrineProtocol" dataDxfId="80"/>
+    <tableColumn id="14" xr3:uid="{FFC67209-2250-E746-B101-892855B7723E}" name="BloodComponents" dataDxfId="79"/>
+    <tableColumn id="9" xr3:uid="{D33BD4F6-DBB2-CB4B-BB20-3BF2C38C6B15}" name="Country" dataDxfId="78"/>
+    <tableColumn id="10" xr3:uid="{90B3A5BF-6BFB-1B47-9F2C-3B2E0DD27E9C}" name="Sex" dataDxfId="77"/>
+    <tableColumn id="16" xr3:uid="{790D0C3F-38B9-454C-B087-1E30344494A3}" name="ADHDtakesMed" dataDxfId="76"/>
+    <tableColumn id="11" xr3:uid="{E0938665-DA8D-7A47-8819-689E53C8E13D}" name="ADHDassess" dataDxfId="75"/>
+    <tableColumn id="12" xr3:uid="{64C2D0D2-8ADC-E44C-8D2D-EBFCFD68558C}" name="AssayMethod" dataDxfId="74"/>
+    <tableColumn id="13" xr3:uid="{8B3BF2BF-7462-0548-99A9-3E81F4AC0BCD}" name="StudyQuality" dataDxfId="73"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CBF1D970-2AD5-0C4A-8747-9F55B010A594}" name="Table3" displayName="Table3" ref="A1:P16" totalsRowShown="0" headerRowDxfId="91" dataDxfId="90">
-  <autoFilter ref="A1:P16" xr:uid="{CBF1D970-2AD5-0C4A-8747-9F55B010A594}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P16">
-    <sortCondition ref="H1:H16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CBF1D970-2AD5-0C4A-8747-9F55B010A594}" name="Table3" displayName="Table3" ref="A1:P17" totalsRowShown="0" headerRowDxfId="72" dataDxfId="71">
+  <autoFilter ref="A1:P17" xr:uid="{CBF1D970-2AD5-0C4A-8747-9F55B010A594}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P17">
+    <sortCondition ref="H1:H17"/>
   </sortState>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{143F8BCE-BA03-8645-B126-D864C3F7DF43}" name="Study" dataDxfId="89"/>
-    <tableColumn id="2" xr3:uid="{32CDE362-AABB-D543-AA1F-C142DB0C60EB}" name="n.e." dataDxfId="88"/>
-    <tableColumn id="3" xr3:uid="{8E4FF48D-BFA7-1143-B619-8E95EBC8EEAF}" name="mean.e." dataDxfId="87"/>
-    <tableColumn id="4" xr3:uid="{BFF231F6-8CBC-B149-A430-D165504830E2}" name="sd.e." dataDxfId="86"/>
-    <tableColumn id="5" xr3:uid="{9DD37156-0CC1-2A4C-9155-31E00CA5AD10}" name="n.c." dataDxfId="85"/>
-    <tableColumn id="6" xr3:uid="{F6B7B7F3-B2C3-C946-A3F1-72F0EA1EF97F}" name="mean.c." dataDxfId="84"/>
-    <tableColumn id="7" xr3:uid="{48BF2315-0559-FF46-A397-14FECA070AFA}" name="sd.c." dataDxfId="83"/>
-    <tableColumn id="8" xr3:uid="{2FC2DB58-2308-7940-90BD-3ADC2F08E235}" name="Sample" dataDxfId="82"/>
-    <tableColumn id="14" xr3:uid="{21016EA7-F270-A34D-AB17-0BE3E60C4449}" name="UrineProtocol" dataDxfId="81"/>
-    <tableColumn id="15" xr3:uid="{42E9724E-F6AD-1044-A9F2-6A8A643798E9}" name="BloodComponents" dataDxfId="80"/>
-    <tableColumn id="9" xr3:uid="{7E3A953F-8F0D-484E-ABFC-D563B5FCA509}" name="Country" dataDxfId="79"/>
-    <tableColumn id="10" xr3:uid="{85699521-1CD2-D346-B0C7-3C95396DA128}" name="Sex" dataDxfId="78"/>
-    <tableColumn id="16" xr3:uid="{ABB1378D-054A-3648-99ED-8888DE8F01BE}" name="ADHDtakesMed" dataDxfId="77"/>
-    <tableColumn id="11" xr3:uid="{03F79FA1-3B32-3A44-B13F-B641879DB3FF}" name="ADHDassess" dataDxfId="76"/>
-    <tableColumn id="12" xr3:uid="{772B4E41-3D4B-FE45-83BA-48B132D19F68}" name="AssayMethod" dataDxfId="75"/>
-    <tableColumn id="13" xr3:uid="{C9D63BD0-4ADC-664E-8045-1A2037BECBB0}" name="StudyQuality" dataDxfId="74"/>
+    <tableColumn id="1" xr3:uid="{143F8BCE-BA03-8645-B126-D864C3F7DF43}" name="Study" dataDxfId="70"/>
+    <tableColumn id="2" xr3:uid="{32CDE362-AABB-D543-AA1F-C142DB0C60EB}" name="n.e." dataDxfId="69"/>
+    <tableColumn id="3" xr3:uid="{8E4FF48D-BFA7-1143-B619-8E95EBC8EEAF}" name="mean.e." dataDxfId="68"/>
+    <tableColumn id="4" xr3:uid="{BFF231F6-8CBC-B149-A430-D165504830E2}" name="sd.e." dataDxfId="67"/>
+    <tableColumn id="5" xr3:uid="{9DD37156-0CC1-2A4C-9155-31E00CA5AD10}" name="n.c." dataDxfId="66"/>
+    <tableColumn id="6" xr3:uid="{F6B7B7F3-B2C3-C946-A3F1-72F0EA1EF97F}" name="mean.c." dataDxfId="65"/>
+    <tableColumn id="7" xr3:uid="{48BF2315-0559-FF46-A397-14FECA070AFA}" name="sd.c." dataDxfId="64"/>
+    <tableColumn id="8" xr3:uid="{2FC2DB58-2308-7940-90BD-3ADC2F08E235}" name="Sample" dataDxfId="63"/>
+    <tableColumn id="14" xr3:uid="{21016EA7-F270-A34D-AB17-0BE3E60C4449}" name="UrineProtocol" dataDxfId="62"/>
+    <tableColumn id="15" xr3:uid="{42E9724E-F6AD-1044-A9F2-6A8A643798E9}" name="BloodComponents" dataDxfId="61"/>
+    <tableColumn id="9" xr3:uid="{7E3A953F-8F0D-484E-ABFC-D563B5FCA509}" name="Country" dataDxfId="60"/>
+    <tableColumn id="10" xr3:uid="{85699521-1CD2-D346-B0C7-3C95396DA128}" name="Sex" dataDxfId="59"/>
+    <tableColumn id="16" xr3:uid="{ABB1378D-054A-3648-99ED-8888DE8F01BE}" name="ADHDtakesMed" dataDxfId="58"/>
+    <tableColumn id="11" xr3:uid="{03F79FA1-3B32-3A44-B13F-B641879DB3FF}" name="ADHDassess" dataDxfId="57"/>
+    <tableColumn id="12" xr3:uid="{772B4E41-3D4B-FE45-83BA-48B132D19F68}" name="AssayMethod" dataDxfId="56"/>
+    <tableColumn id="13" xr3:uid="{C9D63BD0-4ADC-664E-8045-1A2037BECBB0}" name="StudyQuality" dataDxfId="55"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{D060E092-4BB3-BF47-BE9A-817BB4932E55}" name="Table4" displayName="Table4" ref="A1:P9" totalsRowShown="0" headerRowDxfId="73" dataDxfId="72" tableBorderDxfId="71">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{D060E092-4BB3-BF47-BE9A-817BB4932E55}" name="Table4" displayName="Table4" ref="A1:P9" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53" tableBorderDxfId="52">
   <autoFilter ref="A1:P9" xr:uid="{D060E092-4BB3-BF47-BE9A-817BB4932E55}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P9">
     <sortCondition ref="H1:H9"/>
   </sortState>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{0B37B0E6-EF4D-5649-90A1-B990A4D7F310}" name="Study" dataDxfId="70"/>
-    <tableColumn id="2" xr3:uid="{5864584A-6E4D-2A4E-9FF5-E0E21897162A}" name="n.e." dataDxfId="69"/>
-    <tableColumn id="3" xr3:uid="{BE46FBC0-0826-1B4C-A7C4-35CEE4938ACB}" name="mean.e." dataDxfId="68"/>
-    <tableColumn id="4" xr3:uid="{15AE502D-D8CC-E14B-B8D3-10AA6FDDB680}" name="sd.e." dataDxfId="67"/>
-    <tableColumn id="5" xr3:uid="{0E810935-E1DA-AD49-8DD9-E8FEF90F49D2}" name="n.c." dataDxfId="66"/>
-    <tableColumn id="6" xr3:uid="{140D6D9A-2D04-BC4B-ACC6-4A1A0DB6EAEE}" name="mean.c." dataDxfId="65"/>
-    <tableColumn id="7" xr3:uid="{782F91B7-5FCC-194F-B8E5-D46B2929AED7}" name="sd.c." dataDxfId="64"/>
-    <tableColumn id="8" xr3:uid="{E4E37A57-1343-7C46-A0FD-01F74CC253B1}" name="Sample" dataDxfId="63"/>
-    <tableColumn id="14" xr3:uid="{6B30FF22-A964-C341-B3E1-89494D85E32D}" name="UrineProtocol" dataDxfId="62"/>
-    <tableColumn id="15" xr3:uid="{769F4771-2CDE-A34D-B2A6-BE430B5EAB1D}" name="BloodComponents" dataDxfId="61"/>
-    <tableColumn id="9" xr3:uid="{9190A6B2-B0F6-5F41-B315-D2119BC1B191}" name="Country" dataDxfId="60"/>
-    <tableColumn id="10" xr3:uid="{2913413C-280C-6F48-92C8-4C55F660636D}" name="Sex" dataDxfId="59"/>
-    <tableColumn id="16" xr3:uid="{D67D4061-12E6-0D49-9088-022A9425CECA}" name="ADHDtakesMed" dataDxfId="58"/>
-    <tableColumn id="11" xr3:uid="{79E0D1B5-1BB5-2C49-86C0-715980DD54E0}" name="ADHDassess" dataDxfId="57"/>
-    <tableColumn id="12" xr3:uid="{45BF36B3-95B6-BE49-8632-DC89319421EB}" name="AssayMethod" dataDxfId="56"/>
-    <tableColumn id="13" xr3:uid="{A58BDA72-34FC-4E45-8302-916AFD9B5042}" name="StudyQuality" dataDxfId="55"/>
+    <tableColumn id="1" xr3:uid="{0B37B0E6-EF4D-5649-90A1-B990A4D7F310}" name="Study" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{5864584A-6E4D-2A4E-9FF5-E0E21897162A}" name="n.e." dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{BE46FBC0-0826-1B4C-A7C4-35CEE4938ACB}" name="mean.e." dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{15AE502D-D8CC-E14B-B8D3-10AA6FDDB680}" name="sd.e." dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{0E810935-E1DA-AD49-8DD9-E8FEF90F49D2}" name="n.c." dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{140D6D9A-2D04-BC4B-ACC6-4A1A0DB6EAEE}" name="mean.c." dataDxfId="46"/>
+    <tableColumn id="7" xr3:uid="{782F91B7-5FCC-194F-B8E5-D46B2929AED7}" name="sd.c." dataDxfId="45"/>
+    <tableColumn id="8" xr3:uid="{E4E37A57-1343-7C46-A0FD-01F74CC253B1}" name="Sample" dataDxfId="44"/>
+    <tableColumn id="14" xr3:uid="{6B30FF22-A964-C341-B3E1-89494D85E32D}" name="UrineProtocol" dataDxfId="43"/>
+    <tableColumn id="15" xr3:uid="{769F4771-2CDE-A34D-B2A6-BE430B5EAB1D}" name="BloodComponents" dataDxfId="42"/>
+    <tableColumn id="9" xr3:uid="{9190A6B2-B0F6-5F41-B315-D2119BC1B191}" name="Country" dataDxfId="41"/>
+    <tableColumn id="10" xr3:uid="{2913413C-280C-6F48-92C8-4C55F660636D}" name="Sex" dataDxfId="40"/>
+    <tableColumn id="16" xr3:uid="{D67D4061-12E6-0D49-9088-022A9425CECA}" name="ADHDtakesMed" dataDxfId="39"/>
+    <tableColumn id="11" xr3:uid="{79E0D1B5-1BB5-2C49-86C0-715980DD54E0}" name="ADHDassess" dataDxfId="38"/>
+    <tableColumn id="12" xr3:uid="{45BF36B3-95B6-BE49-8632-DC89319421EB}" name="AssayMethod" dataDxfId="37"/>
+    <tableColumn id="13" xr3:uid="{A58BDA72-34FC-4E45-8302-916AFD9B5042}" name="StudyQuality" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F0FE0485-BAB1-F448-A2F7-AB6D01BF21A0}" name="Table46" displayName="Table46" ref="A1:O3" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53" tableBorderDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{F0FE0485-BAB1-F448-A2F7-AB6D01BF21A0}" name="Table46" displayName="Table46" ref="A1:O3" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34" tableBorderDxfId="33">
   <autoFilter ref="A1:O3" xr:uid="{D060E092-4BB3-BF47-BE9A-817BB4932E55}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{05F58B3A-0D80-7846-A0D6-D048DBDB5180}" name="Study" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{BACB12C6-EAE0-AA4C-BD82-A58BC0275010}" name="n.e." dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{847B09CC-9C7A-4346-B7BC-A462A10FFFAA}" name="mean.e." dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{C8D8CC6C-2F68-7C44-8E18-C85F99EA35AE}" name="sd.e." dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{39A1B891-F86D-4745-A4CB-FDB719FAAD91}" name="n.c." dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{523682EB-07D1-E548-B7DD-3AC75EC7B696}" name="mean.c." dataDxfId="46"/>
-    <tableColumn id="7" xr3:uid="{6A1352E3-BEA1-F94F-B920-FA88D66CD9EA}" name="sd.c." dataDxfId="45"/>
-    <tableColumn id="8" xr3:uid="{8BC40B86-F171-9244-89F5-026384635EAF}" name="Sample" dataDxfId="44"/>
-    <tableColumn id="14" xr3:uid="{9B51F90A-0650-9443-B500-091F01D19DF2}" name="UrineProtocol" dataDxfId="43"/>
-    <tableColumn id="9" xr3:uid="{3155FD47-8770-934C-890B-B8E8394594FA}" name="Country" dataDxfId="42"/>
-    <tableColumn id="10" xr3:uid="{E1CF96C4-BC43-B744-8A86-E7D8B6275742}" name="Sex" dataDxfId="41"/>
-    <tableColumn id="15" xr3:uid="{E53B7A23-3F24-8E4D-BB47-239BF0B41A10}" name="ADHDtakesMed" dataDxfId="40"/>
-    <tableColumn id="11" xr3:uid="{682F9D2C-0FB9-314E-804A-CF1F104F6B4A}" name="ADHDassess" dataDxfId="39"/>
-    <tableColumn id="12" xr3:uid="{19D48AA8-6A3C-5449-97F7-FC95641E1119}" name="AssayMethod" dataDxfId="38"/>
-    <tableColumn id="13" xr3:uid="{C450BCB8-FCB4-5A4B-8FB7-9D5ACC7701F8}" name="StudyQuality" dataDxfId="37"/>
+    <tableColumn id="1" xr3:uid="{05F58B3A-0D80-7846-A0D6-D048DBDB5180}" name="Study" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{BACB12C6-EAE0-AA4C-BD82-A58BC0275010}" name="n.e." dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{847B09CC-9C7A-4346-B7BC-A462A10FFFAA}" name="mean.e." dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{C8D8CC6C-2F68-7C44-8E18-C85F99EA35AE}" name="sd.e." dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{39A1B891-F86D-4745-A4CB-FDB719FAAD91}" name="n.c." dataDxfId="28"/>
+    <tableColumn id="6" xr3:uid="{523682EB-07D1-E548-B7DD-3AC75EC7B696}" name="mean.c." dataDxfId="27"/>
+    <tableColumn id="7" xr3:uid="{6A1352E3-BEA1-F94F-B920-FA88D66CD9EA}" name="sd.c." dataDxfId="26"/>
+    <tableColumn id="8" xr3:uid="{8BC40B86-F171-9244-89F5-026384635EAF}" name="Sample" dataDxfId="25"/>
+    <tableColumn id="14" xr3:uid="{9B51F90A-0650-9443-B500-091F01D19DF2}" name="UrineProtocol" dataDxfId="24"/>
+    <tableColumn id="9" xr3:uid="{3155FD47-8770-934C-890B-B8E8394594FA}" name="Country" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{E1CF96C4-BC43-B744-8A86-E7D8B6275742}" name="Sex" dataDxfId="22"/>
+    <tableColumn id="15" xr3:uid="{E53B7A23-3F24-8E4D-BB47-239BF0B41A10}" name="ADHDtakesMed" dataDxfId="21"/>
+    <tableColumn id="11" xr3:uid="{682F9D2C-0FB9-314E-804A-CF1F104F6B4A}" name="ADHDassess" dataDxfId="20"/>
+    <tableColumn id="12" xr3:uid="{19D48AA8-6A3C-5449-97F7-FC95641E1119}" name="AssayMethod" dataDxfId="19"/>
+    <tableColumn id="13" xr3:uid="{C450BCB8-FCB4-5A4B-8FB7-9D5ACC7701F8}" name="StudyQuality" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{27F47C2B-179F-DD47-AF45-2EE6B2433743}" name="Table467" displayName="Table467" ref="A1:O6" totalsRowShown="0" headerRowDxfId="36" dataDxfId="35" tableBorderDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{27F47C2B-179F-DD47-AF45-2EE6B2433743}" name="Table467" displayName="Table467" ref="A1:O6" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16" tableBorderDxfId="15">
   <autoFilter ref="A1:O6" xr:uid="{D060E092-4BB3-BF47-BE9A-817BB4932E55}"/>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{19382680-5DA9-9B4D-A5FA-7B0F348E9D7C}" name="Study" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{64AA7BE9-675A-CF44-91A8-F9F70E509A43}" name="n.e." dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{2AF2252E-409D-B247-AAF9-4031A16F505B}" name="mean.e." dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{F5CB9508-4E03-9249-B05B-C6FAE6C7D5CF}" name="sd.e." dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{FC51CF81-10C8-3043-A7FA-055E3A853CCA}" name="n.c." dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{117B5183-3CAB-1F4F-BEFB-03C44B074213}" name="mean.c." dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{B1EC3395-21C7-784F-8548-875940D94FFC}" name="sd.c." dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{406202E0-8EC6-1549-811D-C2373997E70A}" name="Sample" dataDxfId="26"/>
-    <tableColumn id="14" xr3:uid="{2A4371B7-AA68-B04B-B7A6-16A77E041041}" name="UrineProtocol" dataDxfId="25"/>
-    <tableColumn id="9" xr3:uid="{60A73FFF-192D-7848-94CF-2D7532B27BA9}" name="Country" dataDxfId="24"/>
-    <tableColumn id="10" xr3:uid="{65391106-367B-A546-A2E4-00F9DB9403C6}" name="Sex" dataDxfId="23"/>
-    <tableColumn id="15" xr3:uid="{CB4B6744-5D5D-CF48-BAFF-A3F479943082}" name="ADHDtakesMed" dataDxfId="22"/>
-    <tableColumn id="11" xr3:uid="{CB2AC72A-EAAE-DA4E-82F1-72CBA54BE5AF}" name="ADHDassess" dataDxfId="21"/>
-    <tableColumn id="12" xr3:uid="{E0A2D807-3A71-C04B-89DB-7E6F889C3478}" name="AssayMethod" dataDxfId="20"/>
-    <tableColumn id="13" xr3:uid="{C2E6ED88-71EE-D14E-B51D-5EC675F399D5}" name="StudyQuality" dataDxfId="19"/>
+    <tableColumn id="1" xr3:uid="{19382680-5DA9-9B4D-A5FA-7B0F348E9D7C}" name="Study" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{64AA7BE9-675A-CF44-91A8-F9F70E509A43}" name="n.e." dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{2AF2252E-409D-B247-AAF9-4031A16F505B}" name="mean.e." dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{F5CB9508-4E03-9249-B05B-C6FAE6C7D5CF}" name="sd.e." dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{FC51CF81-10C8-3043-A7FA-055E3A853CCA}" name="n.c." dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{117B5183-3CAB-1F4F-BEFB-03C44B074213}" name="mean.c." dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{B1EC3395-21C7-784F-8548-875940D94FFC}" name="sd.c." dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{406202E0-8EC6-1549-811D-C2373997E70A}" name="Sample" dataDxfId="7"/>
+    <tableColumn id="14" xr3:uid="{2A4371B7-AA68-B04B-B7A6-16A77E041041}" name="UrineProtocol" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{60A73FFF-192D-7848-94CF-2D7532B27BA9}" name="Country" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{65391106-367B-A546-A2E4-00F9DB9403C6}" name="Sex" dataDxfId="4"/>
+    <tableColumn id="15" xr3:uid="{CB4B6744-5D5D-CF48-BAFF-A3F479943082}" name="ADHDtakesMed" dataDxfId="3"/>
+    <tableColumn id="11" xr3:uid="{CB2AC72A-EAAE-DA4E-82F1-72CBA54BE5AF}" name="ADHDassess" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{E0A2D807-3A71-C04B-89DB-7E6F889C3478}" name="AssayMethod" dataDxfId="1"/>
+    <tableColumn id="13" xr3:uid="{C2E6ED88-71EE-D14E-B51D-5EC675F399D5}" name="StudyQuality" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C426C899-02C3-144F-9BA7-220676AF98A3}" name="Table4678" displayName="Table4678" ref="A1:P4" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17" tableBorderDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{C426C899-02C3-144F-9BA7-220676AF98A3}" name="Table4678" displayName="Table4678" ref="A1:P4" totalsRowShown="0" headerRowDxfId="127" dataDxfId="126" tableBorderDxfId="125">
   <autoFilter ref="A1:P4" xr:uid="{D060E092-4BB3-BF47-BE9A-817BB4932E55}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P4">
+    <sortCondition ref="H1:H4"/>
+  </sortState>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{C52A26A1-BFC5-6F4F-8EFC-04EE2A93E986}" name="Study" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{9A3EEC04-677D-C24E-BCEE-3D61E7358145}" name="n.e." dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{C24FE4FE-8171-0B4A-95D5-49E6C206BCF4}" name="mean.e." dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{6C3AE81D-ADFB-F94E-9E4F-90FD28138712}" name="sd.e." dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{7853D7F5-2019-1B45-BA8F-FE5F3DF94DD3}" name="n.c." dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{E1C11975-FCF4-C446-87F5-6E3C5E83F2B3}" name="mean.c." dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{5F33ECB7-854D-AB41-8FE2-0F07D610A839}" name="sd.c." dataDxfId="9"/>
-    <tableColumn id="8" xr3:uid="{0AC627DC-9295-2C4F-B543-EE1E122C54E2}" name="Sample" dataDxfId="8"/>
-    <tableColumn id="14" xr3:uid="{BCFFD763-8261-6844-9208-4E1ED4EFF38F}" name="UrineProtocol" dataDxfId="7"/>
-    <tableColumn id="15" xr3:uid="{A32D01D9-400D-084E-B52E-B692354DA6AB}" name="BloodComponents" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{B5D27043-81DB-3D41-BFEC-99473D877E63}" name="Country" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{402304B8-F32F-6341-B437-372E9B14F5DA}" name="Sex" dataDxfId="4"/>
-    <tableColumn id="16" xr3:uid="{865BE9EA-8533-7443-938B-97430C12522B}" name="ADHDtakesMed" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{FD534823-A10E-ED48-BBF2-9FBAB00EC223}" name="ADHDassess" dataDxfId="2"/>
-    <tableColumn id="12" xr3:uid="{64CA10E5-1ED6-A74C-AC0C-F028176ACAF4}" name="AssayMethod" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{C5B2D257-1988-5C4B-B094-738158133559}" name="StudyQuality" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{C52A26A1-BFC5-6F4F-8EFC-04EE2A93E986}" name="Study" dataDxfId="124"/>
+    <tableColumn id="2" xr3:uid="{9A3EEC04-677D-C24E-BCEE-3D61E7358145}" name="n.e." dataDxfId="123"/>
+    <tableColumn id="3" xr3:uid="{C24FE4FE-8171-0B4A-95D5-49E6C206BCF4}" name="mean.e." dataDxfId="122"/>
+    <tableColumn id="4" xr3:uid="{6C3AE81D-ADFB-F94E-9E4F-90FD28138712}" name="sd.e." dataDxfId="121"/>
+    <tableColumn id="5" xr3:uid="{7853D7F5-2019-1B45-BA8F-FE5F3DF94DD3}" name="n.c." dataDxfId="120"/>
+    <tableColumn id="6" xr3:uid="{E1C11975-FCF4-C446-87F5-6E3C5E83F2B3}" name="mean.c." dataDxfId="119"/>
+    <tableColumn id="7" xr3:uid="{5F33ECB7-854D-AB41-8FE2-0F07D610A839}" name="sd.c." dataDxfId="118"/>
+    <tableColumn id="8" xr3:uid="{0AC627DC-9295-2C4F-B543-EE1E122C54E2}" name="Sample" dataDxfId="117"/>
+    <tableColumn id="14" xr3:uid="{BCFFD763-8261-6844-9208-4E1ED4EFF38F}" name="UrineProtocol" dataDxfId="116"/>
+    <tableColumn id="15" xr3:uid="{A32D01D9-400D-084E-B52E-B692354DA6AB}" name="BloodComponents" dataDxfId="115"/>
+    <tableColumn id="9" xr3:uid="{B5D27043-81DB-3D41-BFEC-99473D877E63}" name="Country" dataDxfId="114"/>
+    <tableColumn id="10" xr3:uid="{402304B8-F32F-6341-B437-372E9B14F5DA}" name="Sex" dataDxfId="113"/>
+    <tableColumn id="16" xr3:uid="{865BE9EA-8533-7443-938B-97430C12522B}" name="ADHDtakesMed" dataDxfId="112"/>
+    <tableColumn id="11" xr3:uid="{FD534823-A10E-ED48-BBF2-9FBAB00EC223}" name="ADHDassess" dataDxfId="111"/>
+    <tableColumn id="12" xr3:uid="{64CA10E5-1ED6-A74C-AC0C-F028176ACAF4}" name="AssayMethod" dataDxfId="110"/>
+    <tableColumn id="13" xr3:uid="{C5B2D257-1988-5C4B-B094-738158133559}" name="StudyQuality" dataDxfId="109"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3685,6 +4216,11 @@
   <threadedComment ref="G1" dT="2024-12-10T12:02:59.93" personId="{EEE08FB4-04DE-7041-99E4-318FC1E5A5FD}" id="{37BDA354-75BD-DC4B-953A-70A240B20C1F}">
     <text>The standard deviation in the control group.</text>
   </threadedComment>
+  <threadedComment ref="M1" dT="2026-10-27T19:13:51.23" personId="{EEE08FB4-04DE-7041-99E4-318FC1E5A5FD}" id="{BA6E313E-BF4E-D640-8A1A-7A71E66F4E11}">
+    <text>for cleaner subgroup analysis plots later on:
+- ADHD doesn't take med = No (have taken in the past or are medication-naive)
+- ADHD takes med = Yes (all or almost all)</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -3707,6 +4243,11 @@
   </threadedComment>
   <threadedComment ref="G1" dT="2024-12-10T12:02:59.93" personId="{EEE08FB4-04DE-7041-99E4-318FC1E5A5FD}" id="{BBDA1B18-269C-B14A-8959-C9B8BC608A36}">
     <text>The standard deviation in the control group.</text>
+  </threadedComment>
+  <threadedComment ref="M1" dT="2026-10-27T19:13:51.23" personId="{EEE08FB4-04DE-7041-99E4-318FC1E5A5FD}" id="{24762B07-76B0-404E-A83D-A1906C8F129D}">
+    <text>for later subgroup analysis plots:
+- ADHD doesn't take med = No (have taken in the past or are medication-naive)
+- ADHD takes med = Yes (all or almost all)</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -3731,6 +4272,11 @@
   <threadedComment ref="G1" dT="2024-12-10T12:02:59.93" personId="{EEE08FB4-04DE-7041-99E4-318FC1E5A5FD}" id="{7D08D5B7-DC08-DE41-977A-FCB6F29F9EBE}">
     <text>The standard deviation in the control group.</text>
   </threadedComment>
+  <threadedComment ref="M1" dT="2026-10-27T19:13:51.23" personId="{EEE08FB4-04DE-7041-99E4-318FC1E5A5FD}" id="{229FAAD6-9652-074A-BDC1-E024165C877C}">
+    <text>for later subgroup analysis plots:
+- ADHD doesn't take med = No (have taken in the past or are medication-naive)
+- ADHD takes med = Yes (all or almost all)</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -3753,6 +4299,11 @@
   </threadedComment>
   <threadedComment ref="G1" dT="2024-12-10T12:02:59.93" personId="{EEE08FB4-04DE-7041-99E4-318FC1E5A5FD}" id="{AFF2E13B-B9F2-5C49-8074-7D9788A72720}">
     <text>The standard deviation in the control group.</text>
+  </threadedComment>
+  <threadedComment ref="M1" dT="2026-10-27T19:13:51.23" personId="{EEE08FB4-04DE-7041-99E4-318FC1E5A5FD}" id="{584ABAA7-E4B2-7B41-A591-A05BC065679B}">
+    <text>for later subgroup analysis plots:
+- ADHD doesn't take med = No (have taken in the past or are medication-naive)
+- ADHD takes med = Yes (all or almost all)</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -3777,6 +4328,11 @@
   <threadedComment ref="G1" dT="2024-12-10T12:02:59.93" personId="{EEE08FB4-04DE-7041-99E4-318FC1E5A5FD}" id="{DC2A0D2E-59D3-514E-B774-F4B5E881E37D}">
     <text>The standard deviation in the control group.</text>
   </threadedComment>
+  <threadedComment ref="L1" dT="2026-10-27T19:13:51.23" personId="{EEE08FB4-04DE-7041-99E4-318FC1E5A5FD}" id="{DAB90153-C344-2F4E-9256-29561116DAEE}">
+    <text>for later subgroup analysis plots:
+- ADHD doesn't take med = No (have taken in the past or are medication-naive)
+- ADHD takes med = Yes (but not all)</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -3799,6 +4355,11 @@
   </threadedComment>
   <threadedComment ref="G1" dT="2024-12-10T12:02:59.93" personId="{EEE08FB4-04DE-7041-99E4-318FC1E5A5FD}" id="{826BFB02-C609-5744-B4B4-51285D20839B}">
     <text>The standard deviation in the control group.</text>
+  </threadedComment>
+  <threadedComment ref="L1" dT="2026-10-27T19:13:51.23" personId="{EEE08FB4-04DE-7041-99E4-318FC1E5A5FD}" id="{6C5786C7-36A3-7348-9C15-908D1DA5B5D2}">
+    <text>for later subgroup analysis plots:
+- ADHD doesn't take med = No (have taken in the past or are medication-naive)
+- ADHD takes med = Yes (but not all)</text>
   </threadedComment>
 </ThreadedComments>
 </file>
@@ -3823,15 +4384,21 @@
   <threadedComment ref="G1" dT="2024-12-10T12:02:59.93" personId="{EEE08FB4-04DE-7041-99E4-318FC1E5A5FD}" id="{BFA83703-16AB-D14A-8FE5-2EFF29672654}">
     <text>The standard deviation in the control group.</text>
   </threadedComment>
+  <threadedComment ref="M1" dT="2026-10-27T19:13:51.23" personId="{EEE08FB4-04DE-7041-99E4-318FC1E5A5FD}" id="{A31B8CA7-3F77-0E49-84BD-EC19CE214978}">
+    <text>for later subgroup analysis plots:
+- ADHD doesn't take med = No (have taken in the past or are medication-naive)
+- ADHD takes med = Yes (but not all)</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C3827FA-F642-9145-B4E4-69002022592E}">
-  <dimension ref="A1:P8"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="13.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.1640625" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.1640625" style="2" bestFit="1" customWidth="1"/>
@@ -3839,14 +4406,14 @@
     <col min="6" max="6" width="12.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="43" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="23" style="2" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="13.33203125" style="2"/>
   </cols>
   <sheetData>
@@ -3876,10 +4443,10 @@
         <v>7</v>
       </c>
       <c r="I1" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>18</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>19</v>
       </c>
       <c r="K1" s="9" t="s">
         <v>12</v>
@@ -3888,7 +4455,7 @@
         <v>14</v>
       </c>
       <c r="M1" s="12" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="N1" s="9" t="s">
         <v>13</v>
@@ -3902,7 +4469,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B2" s="4">
         <v>12</v>
@@ -3929,28 +4496,28 @@
       <c r="J2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>27</v>
+      <c r="K2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>17</v>
+        <v>67</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>32</v>
+        <v>23</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>49</v>
+      <c r="A3" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="B3" s="4">
         <v>50</v>
@@ -3977,28 +4544,28 @@
       <c r="J3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>29</v>
+      <c r="K3" s="3" t="s">
+        <v>61</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>20</v>
+        <v>67</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>31</v>
+        <v>23</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>50</v>
+      <c r="A4" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="B4" s="4">
         <v>180</v>
@@ -4025,211 +4592,259 @@
       <c r="J4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>27</v>
+      <c r="K4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="M4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="N4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>31</v>
+      <c r="P4" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B5" s="4">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C5" s="4">
-        <v>211.72</v>
+        <v>70.099999999999994</v>
       </c>
       <c r="D5" s="4">
-        <v>0.23699999999999999</v>
+        <v>55.34</v>
       </c>
       <c r="E5" s="4">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F5" s="4">
-        <v>151.87</v>
+        <v>90.7</v>
       </c>
       <c r="G5" s="4">
-        <v>67.37</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="6"/>
-      <c r="K5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>26</v>
+        <v>37.630000000000003</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I5" s="6"/>
+      <c r="J5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="N5" s="4" t="s">
-        <v>17</v>
+      <c r="N5" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>31</v>
+        <v>23</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>47</v>
+      <c r="A6" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="B6" s="4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C6" s="4">
-        <v>126</v>
+        <v>211.72</v>
       </c>
       <c r="D6" s="4">
-        <v>44.6</v>
+        <v>0.23699999999999999</v>
       </c>
       <c r="E6" s="4">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F6" s="4">
-        <v>154</v>
+        <v>151.87</v>
       </c>
       <c r="G6" s="4">
-        <v>64.2</v>
+        <v>67.37</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J6" s="6"/>
+      <c r="K6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="6"/>
-      <c r="K6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>26</v>
-      </c>
       <c r="M6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O6" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="N6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>31</v>
+      <c r="P6" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B7" s="4">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C7" s="4">
-        <v>19.7</v>
+        <v>126</v>
       </c>
       <c r="D7" s="4">
-        <v>7.1</v>
+        <v>44.6</v>
       </c>
       <c r="E7" s="4">
         <v>16</v>
       </c>
       <c r="F7" s="4">
-        <v>24.6</v>
+        <v>154</v>
       </c>
       <c r="G7" s="4">
-        <v>9</v>
+        <v>64.2</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J7" s="6"/>
+      <c r="K7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="6"/>
-      <c r="K7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>26</v>
-      </c>
       <c r="M7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>17</v>
+        <v>67</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>31</v>
+        <v>23</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B8" s="4">
         <v>15</v>
       </c>
       <c r="C8" s="4">
-        <v>49.75</v>
+        <v>19.7</v>
       </c>
       <c r="D8" s="4">
-        <v>41.7</v>
+        <v>7.1</v>
       </c>
       <c r="E8" s="4">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F8" s="4">
-        <v>66.64</v>
+        <v>24.6</v>
       </c>
       <c r="G8" s="4">
-        <v>90.08</v>
+        <v>9</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" s="6"/>
+      <c r="K8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J8" s="6"/>
-      <c r="K8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="4" t="s">
-        <v>17</v>
+      <c r="M8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>32</v>
+        <v>23</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A9" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="4">
+        <v>15</v>
+      </c>
+      <c r="C9" s="4">
+        <v>49.75</v>
+      </c>
+      <c r="D9" s="4">
+        <v>41.7</v>
+      </c>
+      <c r="E9" s="4">
+        <v>20</v>
+      </c>
+      <c r="F9" s="4">
+        <v>66.64</v>
+      </c>
+      <c r="G9" s="4">
+        <v>90.08</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" s="6"/>
+      <c r="K9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -4243,10 +4858,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A05ED00E-7F25-AD4B-A28B-169FC96578A4}">
-  <dimension ref="A1:P13"/>
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="17.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -4254,14 +4870,14 @@
     <col min="6" max="6" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="43" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
@@ -4290,10 +4906,10 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>12</v>
@@ -4301,8 +4917,8 @@
       <c r="L1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>61</v>
+      <c r="M1" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>13</v>
@@ -4315,8 +4931,8 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
-        <v>55</v>
+      <c r="A2" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="B2" s="4">
         <v>21</v>
@@ -4344,25 +4960,25 @@
         <v>10</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="15"/>
+        <v>60</v>
+      </c>
+      <c r="L2" s="14"/>
       <c r="M2" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="N2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="P2" s="4" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>46</v>
+      <c r="A3" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="B3" s="4">
         <v>12</v>
@@ -4390,27 +5006,27 @@
         <v>10</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>17</v>
+        <v>67</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>56</v>
+      <c r="A4" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="B4" s="4">
         <v>17</v>
@@ -4418,8 +5034,8 @@
       <c r="C4" s="4">
         <v>229</v>
       </c>
-      <c r="D4" s="4">
-        <v>27</v>
+      <c r="D4" s="16">
+        <v>111.32</v>
       </c>
       <c r="E4" s="4">
         <v>11</v>
@@ -4427,8 +5043,8 @@
       <c r="F4" s="4">
         <v>223</v>
       </c>
-      <c r="G4" s="4">
-        <v>33</v>
+      <c r="G4" s="16">
+        <v>109.45</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>8</v>
@@ -4438,27 +5054,27 @@
         <v>10</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="N4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>17</v>
+      <c r="N4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>43</v>
+      <c r="A5" s="7" t="s">
+        <v>48</v>
       </c>
       <c r="B5" s="4">
         <v>14</v>
@@ -4486,402 +5102,450 @@
         <v>10</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>17</v>
+        <v>67</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="B6" s="4">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C6" s="4">
-        <v>0.38700000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="D6" s="4">
-        <v>0.20899999999999999</v>
+        <v>102.77</v>
       </c>
       <c r="E6" s="4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F6" s="4">
-        <v>0.28899999999999998</v>
+        <v>75.599999999999994</v>
       </c>
       <c r="G6" s="4">
-        <v>0.155</v>
+        <v>29.09</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="I6" s="6"/>
+      <c r="J6" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="K6" s="4" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M6" s="15"/>
-      <c r="N6" s="4" t="s">
-        <v>17</v>
+        <v>62</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="P6" s="8" t="s">
-        <v>31</v>
+        <v>23</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>51</v>
+      <c r="A7" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="B7" s="4">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C7" s="4">
-        <v>14.52</v>
+        <v>0.38700000000000001</v>
       </c>
       <c r="D7" s="4">
-        <v>7.55</v>
+        <v>0.20899999999999999</v>
       </c>
       <c r="E7" s="4">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F7" s="4">
-        <v>12.18</v>
+        <v>0.28899999999999998</v>
       </c>
       <c r="G7" s="4">
-        <v>5.59</v>
+        <v>0.155</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="M7" s="14"/>
+      <c r="N7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="B8" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C8" s="4">
-        <v>1</v>
+        <v>14.52</v>
       </c>
       <c r="D8" s="4">
-        <v>0.6</v>
+        <v>7.55</v>
       </c>
       <c r="E8" s="4">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F8" s="4">
-        <v>1.8</v>
+        <v>12.18</v>
       </c>
       <c r="G8" s="4">
-        <v>0.7</v>
+        <v>5.59</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O8" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="N8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="P8" s="8" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="B9" s="4">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C9" s="4">
-        <v>4.0999999999999996</v>
+        <v>1</v>
       </c>
       <c r="D9" s="4">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="E9" s="4">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F9" s="4">
-        <v>7</v>
+        <v>1.8</v>
       </c>
       <c r="G9" s="4">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>17</v>
+        <v>67</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B10" s="4">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C10" s="4">
-        <v>0.7</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="D10" s="4">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="E10" s="4">
         <v>16</v>
       </c>
       <c r="F10" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G10" s="4">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>17</v>
+        <v>67</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="2">
-        <v>200</v>
-      </c>
-      <c r="C11" s="2">
-        <v>219.13499999999999</v>
-      </c>
-      <c r="D11" s="2">
-        <v>165.4932</v>
+        <v>25</v>
+      </c>
+      <c r="B11" s="4">
+        <v>15</v>
+      </c>
+      <c r="C11" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0.3</v>
       </c>
       <c r="E11" s="4">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="F11" s="4">
-        <v>278</v>
+        <v>1</v>
       </c>
       <c r="G11" s="4">
-        <v>173</v>
+        <v>0.5</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="J11" s="6"/>
       <c r="K11" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="O11" s="8" t="s">
-        <v>30</v>
+        <v>68</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" s="4">
-        <v>31</v>
-      </c>
-      <c r="C12" s="4">
-        <v>4.1500000000000004</v>
-      </c>
-      <c r="D12" s="4">
-        <v>2.57</v>
+        <v>35</v>
+      </c>
+      <c r="B12" s="2">
+        <v>200</v>
+      </c>
+      <c r="C12" s="2">
+        <v>219.13499999999999</v>
+      </c>
+      <c r="D12" s="2">
+        <v>165.4932</v>
       </c>
       <c r="E12" s="4">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="F12" s="4">
-        <v>3.56</v>
+        <v>278</v>
       </c>
       <c r="G12" s="4">
-        <v>1.65</v>
+        <v>173</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>20</v>
+        <v>67</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="B13" s="4">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="C13" s="4">
-        <v>10.130000000000001</v>
-      </c>
-      <c r="D13" s="14">
-        <v>5.7380000000000004</v>
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="D13" s="4">
+        <v>2.57</v>
       </c>
       <c r="E13" s="4">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F13" s="4">
-        <v>2.09</v>
-      </c>
-      <c r="G13" s="14">
-        <v>0.78300000000000003</v>
+        <v>3.56</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1.65</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="J13" s="6"/>
       <c r="K13" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M13" s="15"/>
-      <c r="N13" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="4">
+        <v>57</v>
+      </c>
+      <c r="C14" s="4">
+        <v>10.130000000000001</v>
+      </c>
+      <c r="D14" s="16">
+        <v>5.7380000000000004</v>
+      </c>
+      <c r="E14" s="4">
         <v>17</v>
       </c>
-      <c r="O13" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="P13" s="8" t="s">
-        <v>31</v>
+      <c r="F14" s="4">
+        <v>2.09</v>
+      </c>
+      <c r="G14" s="16">
+        <v>0.78300000000000003</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J14" s="6"/>
+      <c r="K14" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="M14" s="14"/>
+      <c r="N14" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -4895,10 +5559,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43B60205-6DA2-CD47-A100-FC90A70999D8}">
-  <dimension ref="A1:P16"/>
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="17.33203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.5" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -4906,14 +5571,14 @@
     <col min="6" max="6" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="43" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
@@ -4942,10 +5607,10 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>12</v>
@@ -4953,8 +5618,8 @@
       <c r="L1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>61</v>
+      <c r="M1" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>13</v>
@@ -4967,8 +5632,8 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>57</v>
+      <c r="A2" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="B2" s="4">
         <v>15</v>
@@ -4996,27 +5661,27 @@
         <v>10</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="O2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>55</v>
+      <c r="A3" s="3" t="s">
+        <v>46</v>
       </c>
       <c r="B3" s="4">
         <v>21</v>
@@ -5044,25 +5709,25 @@
         <v>10</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="15"/>
+        <v>60</v>
+      </c>
+      <c r="L3" s="14"/>
       <c r="M3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="N3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="P3" s="4" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
-        <v>46</v>
+      <c r="A4" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="B4" s="4">
         <v>12</v>
@@ -5090,27 +5755,27 @@
         <v>10</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>17</v>
+        <v>67</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
-        <v>56</v>
+      <c r="A5" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="B5" s="4">
         <v>17</v>
@@ -5118,8 +5783,8 @@
       <c r="C5" s="4">
         <v>1.55</v>
       </c>
-      <c r="D5" s="4">
-        <v>0.15</v>
+      <c r="D5" s="16">
+        <v>0.62</v>
       </c>
       <c r="E5" s="4">
         <v>11</v>
@@ -5127,8 +5792,8 @@
       <c r="F5" s="4">
         <v>1.79</v>
       </c>
-      <c r="G5" s="4">
-        <v>0.19</v>
+      <c r="G5" s="16">
+        <v>0.63</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>8</v>
@@ -5138,27 +5803,27 @@
         <v>10</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>17</v>
+        <v>68</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>43</v>
+      <c r="A6" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="B6" s="4">
         <v>14</v>
@@ -5186,27 +5851,27 @@
         <v>10</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>17</v>
+        <v>67</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
-        <v>49</v>
+      <c r="A7" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="B7" s="4">
         <v>50</v>
@@ -5234,27 +5899,27 @@
         <v>10</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>20</v>
+        <v>67</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>50</v>
+    <row r="8" spans="1:16" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="B8" s="4">
         <v>180</v>
@@ -5282,402 +5947,450 @@
         <v>11</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="M8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O8" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="N8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="P8" s="4" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
-        <v>59</v>
+      <c r="A9" s="3" t="s">
+        <v>45</v>
       </c>
       <c r="B9" s="4">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C9" s="4">
-        <v>1.127</v>
+        <v>306.2</v>
       </c>
       <c r="D9" s="4">
-        <v>0.38100000000000001</v>
+        <v>202.07</v>
       </c>
       <c r="E9" s="4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" s="4">
-        <v>1.036</v>
+        <v>330.2</v>
       </c>
       <c r="G9" s="4">
-        <v>0.38100000000000001</v>
+        <v>127.76</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="6"/>
+        <v>8</v>
+      </c>
+      <c r="I9" s="6"/>
+      <c r="J9" s="4" t="s">
+        <v>11</v>
+      </c>
       <c r="K9" s="4" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M9" s="15"/>
-      <c r="N9" s="4" t="s">
-        <v>17</v>
+        <v>62</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>51</v>
+      <c r="A10" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="B10" s="4">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C10" s="4">
-        <v>31.21</v>
+        <v>1.127</v>
       </c>
       <c r="D10" s="4">
-        <v>12.84</v>
+        <v>0.38100000000000001</v>
       </c>
       <c r="E10" s="4">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F10" s="4">
-        <v>17.190000000000001</v>
+        <v>1.036</v>
       </c>
       <c r="G10" s="4">
-        <v>6.65</v>
+        <v>0.38100000000000001</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="M10" s="14"/>
+      <c r="N10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="B11" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C11" s="4">
-        <v>11.2</v>
+        <v>31.21</v>
       </c>
       <c r="D11" s="4">
-        <v>17.2</v>
+        <v>12.84</v>
       </c>
       <c r="E11" s="4">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F11" s="4">
-        <v>10.5</v>
+        <v>17.190000000000001</v>
       </c>
       <c r="G11" s="4">
-        <v>4.5</v>
+        <v>6.65</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="J11" s="6"/>
       <c r="K11" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O11" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="N11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="O11" s="4" t="s">
-        <v>30</v>
-      </c>
       <c r="P11" s="4" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="B12" s="4">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C12" s="4">
-        <v>13.7</v>
+        <v>11.2</v>
       </c>
       <c r="D12" s="4">
-        <v>6</v>
+        <v>17.2</v>
       </c>
       <c r="E12" s="4">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F12" s="4">
-        <v>22.1</v>
+        <v>10.5</v>
       </c>
       <c r="G12" s="4">
-        <v>13.6</v>
+        <v>4.5</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>17</v>
+        <v>67</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B13" s="4">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C13" s="4">
-        <v>2.2999999999999998</v>
+        <v>13.7</v>
       </c>
       <c r="D13" s="4">
-        <v>0.9</v>
+        <v>6</v>
       </c>
       <c r="E13" s="4">
         <v>16</v>
       </c>
       <c r="F13" s="4">
-        <v>2.8</v>
+        <v>22.1</v>
       </c>
       <c r="G13" s="4">
-        <v>1.1000000000000001</v>
+        <v>13.6</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="J13" s="6"/>
       <c r="K13" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>17</v>
+        <v>67</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="2">
-        <v>200</v>
-      </c>
-      <c r="C14" s="2">
-        <v>931.56</v>
-      </c>
-      <c r="D14" s="2">
-        <v>480.4425</v>
+        <v>25</v>
+      </c>
+      <c r="B14" s="4">
+        <v>15</v>
+      </c>
+      <c r="C14" s="4">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0.9</v>
       </c>
       <c r="E14" s="4">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="F14" s="4">
-        <v>1060</v>
+        <v>2.8</v>
       </c>
       <c r="G14" s="4">
-        <v>500</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="N14" s="4" t="s">
-        <v>20</v>
+        <v>68</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="P14" s="4" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15" s="4">
-        <v>31</v>
-      </c>
-      <c r="C15" s="4">
-        <v>26.1</v>
-      </c>
-      <c r="D15" s="4">
-        <v>10.47</v>
+        <v>35</v>
+      </c>
+      <c r="B15" s="2">
+        <v>200</v>
+      </c>
+      <c r="C15" s="2">
+        <v>931.56</v>
+      </c>
+      <c r="D15" s="2">
+        <v>480.4425</v>
       </c>
       <c r="E15" s="4">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="F15" s="4">
-        <v>24.46</v>
+        <v>1060</v>
       </c>
       <c r="G15" s="4">
-        <v>9.49</v>
+        <v>500</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="N15" s="4" t="s">
-        <v>20</v>
+        <v>67</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="B16" s="4">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="C16" s="4">
-        <v>22.51</v>
-      </c>
-      <c r="D16" s="14">
-        <v>9.9659999999999993</v>
+        <v>26.1</v>
+      </c>
+      <c r="D16" s="4">
+        <v>10.47</v>
       </c>
       <c r="E16" s="4">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F16" s="4">
-        <v>15.55</v>
-      </c>
-      <c r="G16" s="14">
-        <v>4.37</v>
+        <v>24.46</v>
+      </c>
+      <c r="G16" s="4">
+        <v>9.49</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>9</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="J16" s="6"/>
       <c r="K16" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M16" s="15"/>
-      <c r="N16" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="P16" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="4">
+        <v>57</v>
+      </c>
+      <c r="C17" s="4">
+        <v>22.51</v>
+      </c>
+      <c r="D17" s="16">
+        <v>9.9659999999999993</v>
+      </c>
+      <c r="E17" s="4">
         <v>17</v>
       </c>
-      <c r="O16" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="P16" s="4" t="s">
-        <v>31</v>
+      <c r="F17" s="4">
+        <v>15.55</v>
+      </c>
+      <c r="G17" s="16">
+        <v>4.37</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J17" s="6"/>
+      <c r="K17" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="M17" s="14"/>
+      <c r="N17" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -5692,10 +6405,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ADEFAEB-C733-A348-873D-362FE059BF2E}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="19" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.1640625" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.1640625" style="2" bestFit="1" customWidth="1"/>
@@ -5703,14 +6417,14 @@
     <col min="6" max="6" width="12.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="43" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.6640625" style="2" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="19" style="2"/>
   </cols>
   <sheetData>
@@ -5740,10 +6454,10 @@
         <v>7</v>
       </c>
       <c r="I1" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>18</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>19</v>
       </c>
       <c r="K1" s="9" t="s">
         <v>12</v>
@@ -5751,8 +6465,8 @@
       <c r="L1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="9" t="s">
-        <v>61</v>
+      <c r="M1" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="N1" s="9" t="s">
         <v>13</v>
@@ -5766,7 +6480,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B2" s="4">
         <v>55</v>
@@ -5791,28 +6505,28 @@
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="15"/>
+        <v>60</v>
+      </c>
+      <c r="L2" s="14"/>
       <c r="M2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>64</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>34</v>
+      <c r="A3" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="B3" s="2">
         <v>127</v>
@@ -5837,28 +6551,28 @@
       </c>
       <c r="I3" s="6"/>
       <c r="J3" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="15"/>
+        <v>60</v>
+      </c>
+      <c r="L3" s="14"/>
       <c r="M3" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>17</v>
+        <v>68</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>35</v>
+      <c r="A4" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="B4" s="2">
         <v>84</v>
@@ -5886,27 +6600,27 @@
         <v>11</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>20</v>
+        <v>67</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>36</v>
+      <c r="A5" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="B5" s="4">
         <v>136</v>
@@ -5934,27 +6648,27 @@
         <v>11</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>20</v>
+        <v>67</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>37</v>
+      <c r="A6" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="B6" s="4">
         <v>216</v>
@@ -5979,28 +6693,28 @@
       </c>
       <c r="I6" s="6"/>
       <c r="J6" s="4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M6" s="15"/>
-      <c r="N6" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="M6" s="14"/>
+      <c r="N6" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
-        <v>38</v>
+      <c r="A7" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="B7" s="4">
         <v>56</v>
@@ -6008,7 +6722,7 @@
       <c r="C7" s="4">
         <v>121.7</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="16">
         <v>30.306999999999999</v>
       </c>
       <c r="E7" s="4">
@@ -6017,7 +6731,7 @@
       <c r="F7" s="4">
         <v>85.64</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="16">
         <v>13.31</v>
       </c>
       <c r="H7" s="4" t="s">
@@ -6025,28 +6739,28 @@
       </c>
       <c r="I7" s="6"/>
       <c r="J7" s="4" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M7" s="15"/>
-      <c r="N7" s="4" t="s">
-        <v>17</v>
+        <v>62</v>
+      </c>
+      <c r="M7" s="14"/>
+      <c r="N7" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="P7" s="4" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
-        <v>39</v>
+      <c r="A8" s="7" t="s">
+        <v>56</v>
       </c>
       <c r="B8" s="4">
         <v>269</v>
@@ -6071,30 +6785,30 @@
       </c>
       <c r="I8" s="6"/>
       <c r="J8" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>17</v>
+        <v>67</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="O8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="P8" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="B9" s="4">
         <v>15</v>
@@ -6118,22 +6832,22 @@
         <v>9</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="4" t="s">
-        <v>17</v>
+        <v>60</v>
+      </c>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="P9" s="4" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -6148,6 +6862,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84AE2926-2866-FC45-857B-8E6A5AD06FAC}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:O3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -6194,7 +6909,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>12</v>
@@ -6202,8 +6917,8 @@
       <c r="K1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="9" t="s">
-        <v>61</v>
+      <c r="L1" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="M1" s="9" t="s">
         <v>13</v>
@@ -6217,7 +6932,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B2" s="4">
         <v>12</v>
@@ -6241,30 +6956,30 @@
         <v>9</v>
       </c>
       <c r="I2" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>26</v>
-      </c>
       <c r="L2" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>17</v>
+        <v>67</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="N2" s="8" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="B3" s="4">
         <v>15</v>
@@ -6288,25 +7003,25 @@
         <v>9</v>
       </c>
       <c r="I3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="K3" s="8" t="s">
         <v>22</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>26</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M3" s="8" t="s">
-        <v>17</v>
+      <c r="M3" s="3" t="s">
+        <v>66</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -6321,8 +7036,9 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71B8995B-DB5A-8A4B-A056-4FE5FC1A81DB}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:O6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="13.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="13.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.1640625" style="2" bestFit="1" customWidth="1"/>
@@ -6332,14 +7048,14 @@
     <col min="6" max="6" width="12.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="43" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="26.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="13.5" style="2"/>
+    <col min="15" max="15" width="20.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="13.1640625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
@@ -6368,7 +7084,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J1" s="9" t="s">
         <v>12</v>
@@ -6376,8 +7092,8 @@
       <c r="K1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="L1" s="9" t="s">
-        <v>61</v>
+      <c r="L1" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="M1" s="9" t="s">
         <v>13</v>
@@ -6391,7 +7107,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="B2" s="4">
         <v>15</v>
@@ -6415,30 +7131,30 @@
         <v>9</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M2" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" s="8" t="s">
-        <v>17</v>
+      <c r="M2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="N2" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="O2" s="10" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B3" s="4">
         <v>21</v>
@@ -6462,30 +7178,30 @@
         <v>9</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="L3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="N3" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="M3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="N3" s="8" t="s">
-        <v>17</v>
-      </c>
       <c r="O3" s="8" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B4" s="4">
         <v>28</v>
@@ -6509,28 +7225,28 @@
         <v>9</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" s="16"/>
-      <c r="M4" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="N4" s="8" t="s">
-        <v>17</v>
+        <v>22</v>
+      </c>
+      <c r="L4" s="15"/>
+      <c r="M4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="N4" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B5" s="4">
         <v>37</v>
@@ -6554,28 +7270,28 @@
         <v>9</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>21</v>
+        <v>58</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="K5" s="13"/>
       <c r="L5" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M5" s="4" t="s">
-        <v>20</v>
+      <c r="M5" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="O5" s="8" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="B6" s="4">
         <v>40</v>
@@ -6599,25 +7315,25 @@
         <v>9</v>
       </c>
       <c r="I6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="K6" s="8" t="s">
         <v>22</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>26</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="M6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>17</v>
+      <c r="M6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N6" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -6631,24 +7347,25 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E1D3956-1B3E-A340-8936-1F989A08542E}">
+  <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="23" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
@@ -6677,10 +7394,10 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>12</v>
@@ -6688,8 +7405,8 @@
       <c r="L1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>61</v>
+      <c r="M1" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>13</v>
@@ -6703,140 +7420,140 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="4">
-        <v>37</v>
-      </c>
-      <c r="C2" s="4">
-        <v>4.3099999999999996</v>
-      </c>
-      <c r="D2" s="4">
-        <v>2.21</v>
-      </c>
-      <c r="E2" s="4">
-        <v>21</v>
-      </c>
-      <c r="F2" s="4">
-        <v>4.38</v>
-      </c>
-      <c r="G2" s="4">
-        <v>5.31</v>
+        <v>57</v>
+      </c>
+      <c r="B2">
+        <v>35</v>
+      </c>
+      <c r="C2">
+        <v>12.836</v>
+      </c>
+      <c r="D2">
+        <v>5.1246999999999998</v>
+      </c>
+      <c r="E2">
+        <v>28</v>
+      </c>
+      <c r="F2">
+        <v>12.327500000000001</v>
+      </c>
+      <c r="G2">
+        <v>5.4257999999999997</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="11"/>
+        <v>8</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="8" t="s">
+        <v>11</v>
+      </c>
       <c r="K2" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="16"/>
-      <c r="M2" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="L2" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="N2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="O2" s="8" t="s">
-        <v>30</v>
+      <c r="M2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O2" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
-        <v>33</v>
+      <c r="A3" s="7" t="s">
+        <v>28</v>
       </c>
       <c r="B3" s="4">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C3" s="4">
-        <v>1087.54</v>
+        <v>4.3099999999999996</v>
       </c>
       <c r="D3" s="4">
-        <v>354.38</v>
+        <v>2.21</v>
       </c>
       <c r="E3" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="4">
-        <v>2093.16</v>
+        <v>4.38</v>
       </c>
       <c r="G3" s="4">
-        <v>1116.6099999999999</v>
+        <v>5.31</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>9</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="J3" s="11"/>
       <c r="K3" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="8" t="s">
-        <v>17</v>
+        <v>61</v>
+      </c>
+      <c r="L3" s="15"/>
+      <c r="M3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>41</v>
       </c>
       <c r="O3" s="8" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="P3" s="8" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4">
-        <v>35</v>
-      </c>
-      <c r="C4">
-        <v>12.836</v>
-      </c>
-      <c r="D4">
-        <v>5.1246999999999998</v>
-      </c>
-      <c r="E4">
-        <v>28</v>
-      </c>
-      <c r="F4">
-        <v>12.327500000000001</v>
-      </c>
-      <c r="G4">
-        <v>5.4257999999999997</v>
+      <c r="A4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="4">
+        <v>15</v>
+      </c>
+      <c r="C4" s="4">
+        <v>1087.54</v>
+      </c>
+      <c r="D4" s="4">
+        <v>354.38</v>
+      </c>
+      <c r="E4" s="4">
+        <v>20</v>
+      </c>
+      <c r="F4" s="4">
+        <v>2093.16</v>
+      </c>
+      <c r="G4" s="4">
+        <v>1116.6099999999999</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="8" t="s">
-        <v>11</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" s="11"/>
       <c r="K4" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="O4" s="8" t="s">
-        <v>17</v>
+        <v>60</v>
+      </c>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="O4" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -6850,15 +7567,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="dc16c798-e9f2-4fa2-9c02-0688d5c4ba16">
@@ -6868,7 +7576,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B892A58A1F6D4142BCB0A94988D3184F" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="761f75930ff3c2a8683909f7b1943cf5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dc16c798-e9f2-4fa2-9c02-0688d5c4ba16" xmlns:ns3="2ff12939-372f-4d5b-8f8a-67cba35cb668" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0f0ba2d2693c0249a9afddf607c360e5" ns2:_="" ns3:_="">
     <xsd:import namespace="dc16c798-e9f2-4fa2-9c02-0688d5c4ba16"/>
@@ -7085,15 +7793,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BEA3084-0082-41ED-9953-CF9748F4C3D1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C0C588A-1870-4EB6-ADB1-EBDF96128D67}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -7110,7 +7819,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5074AD8D-4FDA-424A-8C4A-601CDCA67566}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7127,4 +7836,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BEA3084-0082-41ED-9953-CF9748F4C3D1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>